--- a/process-tracing/fontes/fontes-de-dados.xlsx
+++ b/process-tracing/fontes/fontes-de-dados.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Fontes de dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fontes de dados'!$A$4:$L$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fontes de dados'!$A$4:$L$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +45,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +70,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBEAEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF1F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,6 +138,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -500,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2197,8 +2211,566 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>legislativo</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Resolução nº 101, de 30 de dezembro de 1992 — sanções no processo contra Collor</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>BRASIL. Senado Federal. Resolução nº 101, de 30 de dezembro de 1992. Dispõe sobre sanções no processo de impeachment contra o Presidente da República Fernando Affonso Collor de Mello. Brasília, 1992. Disponível em: https://www2.camara.leg.br/legin/fed/ressen/1992/resolucao-101-30-dezembro-1992-480215-publicacaooriginal-1-pl.html. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>https://www2.camara.leg.br/legin/fed/ressen/1992/resolucao-101-30-dezembro-1992-480215-publicacaooriginal-1-pl.html</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Senado Federal</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>busca web (texto integral)</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>verificado_fonte_oficial</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Fonte de EV-C2-T1-003. Documenta que a perda do cargo foi julgada PREJUDICADA pela renúncia — caso de traducao_institucional em C2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>legislativo</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Diário da Assembleia Nacional Constituinte, 5 out. 1988, p. 14380 — promulgação da CF/88</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>BRASIL. Assembleia Nacional Constituinte. Diário da Assembleia Nacional Constituinte, Brasília, 5 out. 1988, p. 14380. Disponível em: https://www2.camara.leg.br/atividade-legislativa/plenario/discursos/escrevendohistoria/destaque-de-materias/centenario-deputado-ulysses-guimaraes/discurso-de-05101988. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>https://www2.camara.leg.br/atividade-legislativa/plenario/discursos/escrevendohistoria/destaque-de-materias/centenario-deputado-ulysses-guimaraes/discurso-de-05101988</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Assembleia Nacional Constituinte</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>busca web (transcrição)</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>c1;c2</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>verificado_fonte_oficial</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Elo 2 da cadeia C1-&gt;C2 (MI-C1-03). Registra 61.200 emendas parlamentares e 122 populares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>legislativo</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Notas taquigráficas da sessão 091.2.55.O de 17 abr. 2016 — admissibilidade do impeachment</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>BRASIL. Câmara dos Deputados. Notas taquigráficas da sessão 091.2.55.O, 17 abr. 2016. Brasília, 2016. Disponível em: https://www.camara.leg.br/internet/plenario/notas/extraord/2016/4/EV1704161400.pdf. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.camara.leg.br/internet/plenario/notas/extraord/2016/4/EV1704161400.pdf</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Câmara dos Deputados</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>17 abr. 2016</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>download (PDF)</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Documento primário do placar 367x137x7 (MI-C4-01), hoje sustentado em nível 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>legislativo</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Câmara autoriza instauração de processo de impeachment de Dilma com 367 votos a favor e 137 contra</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>BRASIL. Câmara dos Deputados. Câmara autoriza instauração de processo de impeachment de Dilma com 367 votos a favor e 137 contra. Agência Câmara, Brasília, 17 abr. 2016. Disponível em: https://www2.camara.leg.br/camaranoticias/noticias/POLITICA/507325-CAMARA-AUTORIZA-INSTAURACAO-DE-PROCESSO-DE-IMPEACHMENT-DE-DILMA-COM-367-VOTOS-A-FAVOR-E-137-CONTRA.html. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>https://www2.camara.leg.br/camaranoticias/noticias/POLITICA/507325-CAMARA-AUTORIZA-INSTAURACAO-DE-PROCESSO-DE-IMPEACHMENT-DE-DILMA-COM-367-VOTOS-A-FAVOR-E-137-CONTRA.html</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Câmara dos Deputados</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>busca web</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>verificado_fonte_oficial</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Fonte de EV-C4-T1-004. Adesão de 22 partidos — medida de heterogeneidade da coalizão (H1.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>legislativo</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Dilma Rousseff perde o mandato de presidente da República, mas mantém direitos políticos</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>BRASIL. Senado Federal. Dilma Rousseff perde o mandato de presidente da República, mas mantém direitos políticos. Senado Notícias, Brasília, 31 ago. 2016. Disponível em: https://www12.senado.leg.br/noticias/materias/2016/08/31/dilma-rousseff-perde-o-mandato-de-presidente-da-republica-mas-mantem-direitos-politicos. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>https://www12.senado.leg.br/noticias/materias/2016/08/31/dilma-rousseff-perde-o-mandato-de-presidente-da-republica-mas-mantem-direitos-politicos</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Senado Federal</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>busca web</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>verificado_fonte_oficial</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Fonte de EV-C4-T1-003 (inabilitação 42x36x3). Resolve a divergência 61x20 / 61x21: eram duas votações distintas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>judicial</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Presidente do STF permite votação em separado de inabilitação para funções públicas</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>BRASIL. Câmara dos Deputados. Presidente do STF permite votação em separado de inabilitação para funções públicas. Agência Câmara, Brasília, 31 ago. 2016. Disponível em: https://www.camara.leg.br/noticias/497226-presidente-do-stf-permite-votacao-em-separado-de-inabilitacao-para-funcoes-publicas. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.camara.leg.br/noticias/497226-presidente-do-stf-permite-votacao-em-separado-de-inabilitacao-para-funcoes-publicas</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Câmara dos Deputados / STF</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>busca web</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>verificado_fonte_oficial</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Documenta a decisão que separou as duas votações de 31/08/2016 — origem da divergência aparente nos placares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>legislativo</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Câmara rejeita PEC 37; texto será arquivado</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>BRASIL. Câmara dos Deputados. Câmara rejeita PEC 37; texto será arquivado. Agência Câmara, Brasília, 25 jun. 2013. Disponível em: https://www.camara.leg.br/noticias/407780-camara-rejeita-pec-37-texto-sera-arquivado/. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.camara.leg.br/noticias/407780-camara-rejeita-pec-37-texto-sera-arquivado/</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Câmara dos Deputados</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>busca web</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>c3</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>verificado_fonte_oficial</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Placar refinado: 430 contra, 9 a favor, 2 abstenções. Todos os partidos orientaram pela rejeição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>eleitoral</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Julgados históricos: Collor — eleição de 1989</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>BRASIL. Tribunal Superior Eleitoral. Collor. Julgados históricos. Brasília, [s.d.]. Disponível em: https://www.tse.jus.br/jurisprudencia/julgados-historicos/collor. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>https://www.tse.jus.br/jurisprudencia/julgados-historicos/collor</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Tribunal Superior Eleitoral</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>busca web</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>c1;c2</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>corroborado_imprensa</t>
+        </is>
+      </c>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>Elo 3 da cadeia C1-&gt;C2. Percentuais do 2º turno divergem entre fontes — resolver na totalização oficial do TSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>acervo_institucional</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Nota oficial sobre tarifa de ônibus — Prefeitura de São Paulo</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>SÃO PAULO (Município). Nota oficial sobre tarifa de ônibus. São Paulo, 2013. Disponível em: https://prefeitura.sp.gov.br/w/noticia/nota-oficial-sobre-tarifa-de-onibus. Acesso em: 22 ago. 2026.</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>https://prefeitura.sp.gov.br/w/noticia/nota-oficial-sobre-tarifa-de-onibus</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Prefeitura de São Paulo</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>busca web</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>c3</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Caminho para MI-C3-01. A busca NÃO confirmou a data de 19/06/2013 nem o mecanismo da revogação; confirmado apenas o reajuste de R$3,00 para R$3,20 em 02/06/2013. Recuperar o decreto municipal.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L30"/>
+  <autoFilter ref="A4:L39"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -2229,6 +2801,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
